--- a/ITC.NS.xlsx
+++ b/ITC.NS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1225E-D16C-4B4F-A5A7-559631D21D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192E9280-43E6-45F6-A50C-B02206A690A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{BED34A11-0209-4766-B8A3-A0379845CA49}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{BED34A11-0209-4766-B8A3-A0379845CA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -786,7 +786,7 @@
       <c r="H3" s="4">
         <v>12513.458646999999</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="22" t="s">
         <v>5</v>
       </c>
     </row>
@@ -801,6 +801,7 @@
         <f>+H2*H3</f>
         <v>6074032.8272537999</v>
       </c>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -816,7 +817,7 @@
         <f>13368.18+792.18+4939.51</f>
         <v>19099.870000000003</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="22" t="s">
         <v>5</v>
       </c>
     </row>
